--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_12.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03831687506964364</v>
+        <v>0.0307954426535883</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008472774029021725</v>
+        <v>0.008460309764744066</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>48349445</v>
+        <v>3724409</v>
       </c>
       <c r="L2" t="n">
-        <v>24128567</v>
+        <v>1704582</v>
       </c>
       <c r="M2" t="n">
-        <v>5137237</v>
+        <v>320106</v>
       </c>
       <c r="N2" t="n">
-        <v>156666</v>
+        <v>9555</v>
       </c>
       <c r="O2" t="n">
-        <v>3124546</v>
+        <v>166732</v>
       </c>
       <c r="P2" t="n">
-        <v>1242023</v>
+        <v>66757</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999957680702209</v>
+        <v>0.9999990463256836</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7867429852485657</v>
+        <v>0.7195658683776855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6053019762039185</v>
+        <v>0.5079741477966309</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5027580261230469</v>
+        <v>0.3785123527050018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1244965791702271</v>
+        <v>0.05079042911529541</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5630558133125305</v>
+        <v>0.4334776997566223</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6691418886184692</v>
+        <v>0.5581828951835632</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01055753523378298</v>
+        <v>0.00813149088777337</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002031055628665047</v>
+        <v>0.002026924819488894</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>48349445</v>
+        <v>3724409</v>
       </c>
       <c r="E3" t="n">
-        <v>10963846</v>
+        <v>1158979</v>
       </c>
       <c r="F3" t="n">
-        <v>521434</v>
+        <v>73014</v>
       </c>
       <c r="G3" t="n">
-        <v>46065</v>
+        <v>8894</v>
       </c>
       <c r="H3" t="n">
-        <v>59840</v>
+        <v>6562</v>
       </c>
       <c r="I3" t="n">
-        <v>7530</v>
+        <v>774</v>
       </c>
       <c r="J3" t="n">
-        <v>120199145</v>
+        <v>10069614</v>
       </c>
       <c r="K3" t="n">
-        <v>122901242</v>
+        <v>9991864</v>
       </c>
       <c r="L3" t="n">
-        <v>140734430</v>
+        <v>11411482</v>
       </c>
       <c r="M3" t="n">
-        <v>179632487</v>
+        <v>14944286</v>
       </c>
       <c r="N3" t="n">
-        <v>193779877</v>
+        <v>16147193</v>
       </c>
       <c r="O3" t="n">
-        <v>187404554</v>
+        <v>15684972</v>
       </c>
       <c r="P3" t="n">
-        <v>193018485</v>
+        <v>16169110</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8065202832221985</v>
+        <v>0.7489811182022095</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6110461950302124</v>
+        <v>0.5083065032958984</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4569747447967529</v>
+        <v>0.3383337259292603</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1459268033504486</v>
+        <v>0.1058889999985695</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5100527405738831</v>
+        <v>0.3249363601207733</v>
       </c>
       <c r="W3" t="n">
-        <v>0.534756600856781</v>
+        <v>0.3440195918083191</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.08077822547226479</v>
+        <v>0.06941767934285653</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03202893469858889</v>
+        <v>0.03198862993387096</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1290176</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1704582</v>
+      </c>
+      <c r="F4" t="n">
+        <v>271550</v>
+      </c>
+      <c r="G4" t="n">
+        <v>37546</v>
+      </c>
+      <c r="H4" t="n">
+        <v>43045</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6554</v>
+      </c>
+      <c r="J4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
-        <v>11915632</v>
-      </c>
-      <c r="E4" t="n">
-        <v>24128567</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2743490</v>
-      </c>
-      <c r="G4" t="n">
-        <v>197281</v>
-      </c>
-      <c r="H4" t="n">
-        <v>439349</v>
-      </c>
-      <c r="I4" t="n">
-        <v>62978</v>
-      </c>
-      <c r="J4" t="n">
-        <v>319</v>
-      </c>
       <c r="K4" t="n">
-        <v>13105752</v>
+        <v>1451502</v>
       </c>
       <c r="L4" t="n">
-        <v>15733467</v>
+        <v>1651065</v>
       </c>
       <c r="M4" t="n">
-        <v>5080873</v>
+        <v>525589</v>
       </c>
       <c r="N4" t="n">
-        <v>1101730</v>
+        <v>178571</v>
       </c>
       <c r="O4" t="n">
-        <v>2424719</v>
+        <v>217906</v>
       </c>
       <c r="P4" t="n">
-        <v>614120</v>
+        <v>52840</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999979138374329</v>
+        <v>0.9999995231628418</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7965088486671448</v>
+        <v>0.7339789271354675</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6081605553627014</v>
+        <v>0.5081403255462646</v>
       </c>
       <c r="T4" t="n">
-        <v>0.47877436876297</v>
+        <v>0.3572970628738403</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1343625485897064</v>
+        <v>0.06865161657333374</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5352453589439392</v>
+        <v>0.3714400231838226</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5944489240646362</v>
+        <v>0.42568239569664</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>860682</v>
+        <v>118818</v>
       </c>
       <c r="E5" t="n">
-        <v>3712183</v>
+        <v>357022</v>
       </c>
       <c r="F5" t="n">
-        <v>5137237</v>
+        <v>320106</v>
       </c>
       <c r="G5" t="n">
-        <v>346182</v>
+        <v>49918</v>
       </c>
       <c r="H5" t="n">
-        <v>1030551</v>
+        <v>84877</v>
       </c>
       <c r="I5" t="n">
-        <v>154987</v>
+        <v>15384</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11598761</v>
+        <v>1248225</v>
       </c>
       <c r="L5" t="n">
-        <v>15358736</v>
+        <v>1648871</v>
       </c>
       <c r="M5" t="n">
-        <v>6104603</v>
+        <v>626019</v>
       </c>
       <c r="N5" t="n">
-        <v>916927</v>
+        <v>80681</v>
       </c>
       <c r="O5" t="n">
-        <v>3001381</v>
+        <v>346390</v>
       </c>
       <c r="P5" t="n">
-        <v>1080572</v>
+        <v>127293</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999983906745911</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8739277720451355</v>
+        <v>0.8355429172515869</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8413300514221191</v>
+        <v>0.7989805340766907</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9429181814193726</v>
+        <v>0.9298484325408936</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9896983504295349</v>
+        <v>0.9842073321342468</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9723094701766968</v>
+        <v>0.9656252264976501</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9913516640663147</v>
+        <v>0.9890269637107849</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>202656</v>
+        <v>20740</v>
       </c>
       <c r="E6" t="n">
-        <v>278431</v>
+        <v>27131</v>
       </c>
       <c r="F6" t="n">
-        <v>291465</v>
+        <v>22710</v>
       </c>
       <c r="G6" t="n">
-        <v>156666</v>
+        <v>9555</v>
       </c>
       <c r="H6" t="n">
-        <v>126120</v>
+        <v>8606</v>
       </c>
       <c r="I6" t="n">
-        <v>18182</v>
+        <v>1490</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>115436</v>
+        <v>19782</v>
       </c>
       <c r="E7" t="n">
-        <v>697265</v>
+        <v>95242</v>
       </c>
       <c r="F7" t="n">
-        <v>1362632</v>
+        <v>134812</v>
       </c>
       <c r="G7" t="n">
-        <v>455547</v>
+        <v>67916</v>
       </c>
       <c r="H7" t="n">
-        <v>3124546</v>
+        <v>166732</v>
       </c>
       <c r="I7" t="n">
-        <v>370443</v>
+        <v>28638</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>11346</v>
+        <v>1986</v>
       </c>
       <c r="E8" t="n">
-        <v>81742</v>
+        <v>12691</v>
       </c>
       <c r="F8" t="n">
-        <v>161852</v>
+        <v>23503</v>
       </c>
       <c r="G8" t="n">
-        <v>56655</v>
+        <v>14297</v>
       </c>
       <c r="H8" t="n">
-        <v>768859</v>
+        <v>74816</v>
       </c>
       <c r="I8" t="n">
-        <v>1242023</v>
+        <v>66757</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
